--- a/db/catalog/3-electrocasnice_MU.xlsx
+++ b/db/catalog/3-electrocasnice_MU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produse" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicționar tag-uri" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Produse" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dicționar tag-uri" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Produse'!$A$1:$R$201</definedName>
@@ -1940,11 +1940,7 @@
 Greutate (kg): 32,7</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>https://tmp-hansa.lv.extranet.www.amica.com.pl/files-api/products-pim/manual/Hansa/SER_0015174_KPR/ab5738afa0d81cc75f5fd34ab136737f4665aeb8_SER_0015174_KPR.pdf</t>
-        </is>
-      </c>
+      <c r="O12" s="3" t="n"/>
       <c r="P12" s="3" t="inlineStr">
         <is>
           <t>https://tmp-hansa.lv.extranet.www.amica.com.pl/en/products/cookers/fcmw56069 | https://demax.ro/aragaz-mixt-hansa-fcmw56069-cuptor-electric-67-l-clasa-a-plita-gaz-4-arzatoare-alb.html | https://hansa.ru/product/plita-kombinirovannaya-hansa-fcmw56069</t>
@@ -1957,7 +1953,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare apare doar pe o pagină de listare cu multe produse (oreol.eu), nu pe o pagină dedicată modelului; de verificat pe ambalaj. Specificațiile sunt de pe site-ul Hansa (Amica, Letonia), confirmate de hansa.ru. Volum: producătorul dă 62 l net; retailerii români (Demax, eMAG, evoMAG) scriu 67 l; am folosit valoarea producătorului. hansa.ru se contrazice la timer („Nu” în tabel, timer digital în descriere); am omis timerul. Culoarea albă e confirmată de Demax și hansa.ru. Garanție: Demax indică 24 de luni, fără PF/PJ; am omis-o.</t>
+          <t>Codul de bare apare doar pe o pagină de listare cu multe produse (oreol.eu), nu pe o pagină dedicată modelului; de verificat pe ambalaj. Specificațiile sunt de pe site-ul Hansa (Amica, Letonia), confirmate de hansa.ru. Volum: producătorul dă 62 l net; retailerii români (Demax, eMAG, evoMAG) scriu 67 l; am folosit valoarea producătorului. hansa.ru se contrazice la timer („Nu” în tabel, timer digital în descriere); am omis timerul. Culoarea albă e confirmată de Demax și hansa.ru. Garanție: Demax indică 24 de luni, fără PF/PJ; am omis-o. | 18 oct 2026: link de fișă scos (404 la producător, fără înlocuitor oficial).</t>
         </is>
       </c>
     </row>
@@ -2075,11 +2071,7 @@
 Greutate (kg): 49,1</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>https://tmp-hansa.lv.extranet.www.amica.com.pl/files-api/products-pim/manual/Hansa/SER_0026144_KPR/48d476ebd12ee10d0738afdd955846a80a8aefec_SER_0026144_KPR.pdf</t>
-        </is>
-      </c>
+      <c r="O13" s="3" t="n"/>
       <c r="P13" s="3" t="inlineStr">
         <is>
           <t>https://tmp-hansa.lv.extranet.www.amica.com.pl/en/products/cookers/fcmx5825092 | https://www.kursi.lv/ru/gazovaja-plita-s-jelektricheskoj-duhovkoj-hansa-fcmx5825092 | https://demax.ro/aragaz-hansa-fcmx5825092-4-arzatoare-gaz-cuptor-electric-8-functii-decongelare-steam-cleaning-aprindere-electrica-50-cm-clasa-a-65-litri-argintiu.html</t>
@@ -2092,7 +2084,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare apare pe pagina kursi.lv a modelului FCMX5825092 (găsit prin căutarea exactă a codului; pagina nu a fost deschisă). Specificațiile sunt de pe site-ul Hansa (Amica, Letonia). Titlul Demax indică „8 funcții” și „Steam Cleaning”, iar producătorul 9 funcții și curățare catalitică; am folosit datele producătorului. Culoare: Demax scrie „argintiu”, euronics.ee „oțel inoxidabil”, iar litera X din cod indică varianta inox; am trecut „inox”.</t>
+          <t>Codul de bare apare pe pagina kursi.lv a modelului FCMX5825092 (găsit prin căutarea exactă a codului; pagina nu a fost deschisă). Specificațiile sunt de pe site-ul Hansa (Amica, Letonia). Titlul Demax indică „8 funcții” și „Steam Cleaning”, iar producătorul 9 funcții și curățare catalitică; am folosit datele producătorului. Culoare: Demax scrie „argintiu”, euronics.ee „oțel inoxidabil”, iar litera X din cod indică varianta inox; am trecut „inox”. | 18 oct 2026: link de fișă scos (404 la producător, fără înlocuitor oficial).</t>
         </is>
       </c>
     </row>
@@ -2207,11 +2199,7 @@
 Greutate (kg): 39,95</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>https://tmp-hansa.lv.extranet.www.amica.com.pl/files-api/products-pim/manual/Hansa/SER_0014933_KPR/c2de508154fd942312b67ff002c7fd6513840fe3_SER_0014933_KPR.pdf</t>
-        </is>
-      </c>
+      <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
           <t>https://tmp-hansa.lv.extranet.www.amica.com.pl/en/products/cookers/fcmw581009 | https://www.hinnavaatlus.ee/1798569/hansa-fcmw581009/</t>
@@ -2224,7 +2212,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare apare doar pe un site de comparare a prețurilor (hinnavaatlus.ee, pagina modelului FCMW581009), nu pe pagina unui retailer sau a producătorului; de verificat pe ambalaj. Specificațiile sunt de pe site-ul Hansa (Amica, Letonia). Culoarea nu e precizată explicit de producător (codul intern se termină în „(W)”); am omis-o, de confirmat (probabil alb). Capacul: în tabel scrie „metal”, iar în descriere „sticlă”; l-am omis. Nicio sursă românească citită pentru acest model.</t>
+          <t>Codul de bare apare doar pe un site de comparare a prețurilor (hinnavaatlus.ee, pagina modelului FCMW581009), nu pe pagina unui retailer sau a producătorului; de verificat pe ambalaj. Specificațiile sunt de pe site-ul Hansa (Amica, Letonia). Culoarea nu e precizată explicit de producător (codul intern se termină în „(W)”); am omis-o, de confirmat (probabil alb). Capacul: în tabel scrie „metal”, iar în descriere „sticlă”; l-am omis. Nicio sursă românească citită pentru acest model. | 18 oct 2026: link de fișă scos (404 la producător, fără înlocuitor oficial).</t>
         </is>
       </c>
     </row>
@@ -2337,11 +2325,7 @@
 Greutate (kg): 35,3</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>https://tmp-hansa.lv.extranet.www.amica.com.pl/files-api/products-pim/manual/Hansa/SER_0014926_KPR/e57b5da6dce0ba45180cda16ea42aa881f0c74b3_SER_0014926_KPR.pdf</t>
-        </is>
-      </c>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
           <t>https://tmp-hansa.lv.extranet.www.amica.com.pl/en/products/cookers/fcgx520209</t>
@@ -2354,7 +2338,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare apare doar pe site-uri de manuale (manua.ls, juhend.ee, pagina modelului FCGX520209), nu pe pagina unui retailer sau a producătorului; de verificat pe ambalaj. Specificațiile sunt de pe site-ul Hansa (Amica, Letonia). Culoarea nu e scrisă explicit de producător; sursele care o dădeau „inox” (okazii.ro, 01.ee) au fost eliminate ca nevalide, iar euronics.ee prezintă alt model (FCGX5202092). Am omis culoarea, de confirmat (litera X din cod sugerează inox). Funcțiile cuptorului: producătorul dă „2”; descrierea „încălzire statică, grill” e dedusă din tipul de încălzire „static” și din grill, de confirmat. Aprinderea cuptorului nu e precizată.</t>
+          <t>Codul de bare apare doar pe site-uri de manuale (manua.ls, juhend.ee, pagina modelului FCGX520209), nu pe pagina unui retailer sau a producătorului; de verificat pe ambalaj. Specificațiile sunt de pe site-ul Hansa (Amica, Letonia). Culoarea nu e scrisă explicit de producător; sursele care o dădeau „inox” (okazii.ro, 01.ee) au fost eliminate ca nevalide, iar euronics.ee prezintă alt model (FCGX5202092). Am omis culoarea, de confirmat (litera X din cod sugerează inox). Funcțiile cuptorului: producătorul dă „2”; descrierea „încălzire statică, grill” e dedusă din tipul de încălzire „static” și din grill, de confirmat. Aprinderea cuptorului nu e precizată. | 18 oct 2026: link de fișă scos (404 la producător, fără înlocuitor oficial).</t>
         </is>
       </c>
     </row>
@@ -2419,8 +2403,26 @@
           <t>Harlem, aragaz portabil, electrocasnice, 2 ochiuri</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz portabil Harlem cu 2 ochiuri, pe butelie&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Aragaz de masă cu 2 arzătoare (1,5 kW și 0,9 kW), pentru butelie, cu duzele incluse. Are corp metalic emailat și capac, dimensiuni de 50,5 x 36 x 10 cm și cântărește circa 3 kg — bun pentru casa de vacanță, terasă sau atelier.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Racordarea la butelie se face cu regulator și furtun potrivite. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Brand: Harlem
+Număr arzătoare: 2
+Putere arzătoare (kW): 1,5 și 0,9
+Tip gaz: butelie (GPL), duze incluse
+Dimensiuni (cm): 50,5 x 36 x 10
+Greutate (kg): 3
+Capac: da
+Țara de origine: Turcia</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="6" t="inlineStr">
@@ -2430,7 +2432,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu apare pe nicio pagină care să poată fi citită. O căutare cu ambele coduri Harlem a returnat paginile moyo.ua „Harlem O200-grey” și „Harlem O300-brown”, dar acestea redirecționează spre o listă de categorie, fără cod sau specificații. Harlem are variante O200 și O300 în mai multe culori (vencon.ua: O200 GREY/BROWN, O300 BROWN), iar ERP-ul nu precizează culoarea, deci nu se poate stabili varianta exactă. Denumirea vine doar din ERP („ARAGAZ HARLEM 2 OCHIURI”). De verificat pe ambalaj: model (probabil O200) și culoare.</t>
+          <t>Codul de bare nu apare pe nicio pagină care să poată fi citită. O căutare cu ambele coduri Harlem a returnat paginile moyo.ua „Harlem O200-grey” și „Harlem O300-brown”, dar acestea redirecționează spre o listă de categorie, fără cod sau specificații. Harlem are variante O200 și O300 în mai multe culori (vencon.ua: O200 GREY/BROWN, O300 BROWN), iar ERP-ul nu precizează culoarea, deci nu se poate stabili varianta exactă. Denumirea vine doar din ERP („ARAGAZ HARLEM 2 OCHIURI”). De verificat pe ambalaj: model (probabil O200) și culoare. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -2495,8 +2497,25 @@
           <t>Harlem, aragaz portabil, electrocasnice, 3 ochiuri</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz portabil Harlem cu 3 ochiuri&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Aragaz de masă cu 3 arzătoare (1,9 kW, 1,5 kW și 0,9 kW), cu blat din oțel emailat și capac. Dimensiunile sunt de 63,5 x 38,5 x 12 cm.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Producătorul are variante pentru butelie și pentru gaz natural — îți confirmăm varianta exactă la telefon. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Brand: Harlem
+Număr arzătoare: 3
+Putere arzătoare (kW): 1,9; 1,5; 0,9
+Blat: oțel emailat
+Capac: da
+Dimensiuni (cm): 63,5 x 38,5 x 12
+Țara de origine: Turcia</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr"/>
       <c r="Q17" s="6" t="inlineStr">
@@ -2506,7 +2525,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu apare pe nicio pagină care să poată fi citită. O căutare cu ambele coduri Harlem a returnat paginile moyo.ua „Harlem O200-grey” și „Harlem O300-brown”, dar acestea redirecționează spre o listă de categorie, fără cod sau specificații. Harlem are variante O200 și O300 în mai multe culori (vencon.ua: O200 GREY/BROWN, O300 BROWN), iar ERP-ul nu precizează culoarea, deci nu se poate stabili varianta exactă. Denumirea vine doar din ERP („ARAGAZ HARLEM 3 OCHIURI”). De verificat pe ambalaj: model (probabil O300) și culoare.</t>
+          <t>Codul de bare nu apare pe nicio pagină care să poată fi citită. O căutare cu ambele coduri Harlem a returnat paginile moyo.ua „Harlem O200-grey” și „Harlem O300-brown”, dar acestea redirecționează spre o listă de categorie, fără cod sau specificații. Harlem are variante O200 și O300 în mai multe culori (vencon.ua: O200 GREY/BROWN, O300 BROWN), iar ERP-ul nu precizează culoarea, deci nu se poate stabili varianta exactă. Denumirea vine doar din ERP („ARAGAZ HARLEM 3 OCHIURI”). De verificat pe ambalaj: model (probabil O300) și culoare. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -2822,8 +2841,38 @@
           <t>LDK, aragaz, electrocasnice, bordo, GPL</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz pe gaz de 50 cm, cu 4 arzătoare și cuptor pe gaz&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK 5060 A Bordo LPG are plită cu 4 arzătoare și cuptor pe gaz, în culoarea bordo, cu capac metalic. Varianta este pentru GPL (butelie). Dimensiunile sunt de aproximativ 50 x 60 x 85 cm (lățime x adâncime x înălțime), potrivite pentru bucătării mici. Cuptorul pe gaz are 46 l, iar siguranța la flacără acționează și la plită, și la cuptor.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Arzătoare pentru toate vasele&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Plita are un arzător mare, două arzătoare normale și unul mic. Aprinderea electrică se face cu o apăsare de buton.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Siguranță la flacără&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dacă flacăra se stinge accidental, alimentarea cu gaz se întrerupe automat. La pornire, ține butonul apăsat câteva secunde după aprindere.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Limitări&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Modelul nu are grill, rotisor, ventilator sau lumină în cuptor.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Racordarea la butelie se face de personal autorizat. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Brand: LDK
+Model: 5060 A Bordo LPG
+Alimentare plită: gaz
+Alimentare cuptor: gaz
+Număr arzătoare: 4 (1 mare, 2 normale, 1 mic)
+Tip gaz: GPL
+Aprindere: electrică la plită
+Siguranță gaz: da
+Capac: metalic
+Culoare: bordo
+Dimensiuni (L x A x Î, cm): aprox. 50 x 60 x 85
+Capacitate cuptor (l): 46
+Siguranță gaz: plită și cuptor
+Greutate (kg): 34</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -2837,7 +2886,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 A BORDO LPG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Cea mai apropiată pagină: „5060 A Bordo RMV LPG” (ART6083), dar are RMV în denumire. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact.</t>
+          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 A BORDO LPG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Cea mai apropiată pagină: „5060 A Bordo RMV LPG” (ART6083), dar are RMV în denumire. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -2902,8 +2951,33 @@
           <t>LDK, aragaz, electrocasnice, alb, gaz natural</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz pe gaz de 50 cm, cu 4 arzătoare și cuptor pe gaz&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK 5060 A WH RMV NG are plită cu 4 arzătoare și cuptor pe gaz, în culoarea alb, cu capac metalic. Varianta este pentru gaz natural (de la rețea). Dimensiunile sunt de aproximativ 50 x 60 x 85 cm (lățime x adâncime x înălțime), potrivite pentru bucătării mici.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Arzătoare pentru toate vasele&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Plita are un arzător mare, două arzătoare normale și unul mic. Aprinderea electrică se face cu o apăsare de buton.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Siguranță la flacără&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dacă flacăra se stinge accidental, alimentarea cu gaz se întrerupe automat. La pornire, ține butonul apăsat câteva secunde după aprindere.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Volumul exact al cuptorului diferă între variantele seriei 5060. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Brand: LDK
+Model: 5060 A WH RMV NG
+Alimentare plită: gaz
+Alimentare cuptor: gaz
+Număr arzătoare: 4 (1 mare, 2 normale, 1 mic)
+Tip gaz: gaz natural (NG)
+Aprindere: electrică la plită
+Siguranță gaz: da
+Capac: metalic
+Culoare: alb
+Dimensiuni (L x A x Î, cm): aprox. 50 x 60 x 85</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -2917,7 +2991,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 A WH RMV NG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Producătorul nu are nicio variantă „5060 A” albă. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact.</t>
+          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 A WH RMV NG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Producătorul nu are nicio variantă „5060 A” albă. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -2982,8 +3056,33 @@
           <t>LDK, aragaz, electrocasnice, negru, gaz natural</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz pe gaz de 50 cm, cu 4 arzătoare și cuptor pe gaz&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK 5060 Black NG are plită cu 4 arzătoare și cuptor pe gaz, în culoarea negru, cu capac metalic. Varianta este pentru gaz natural (de la rețea). Dimensiunile sunt de aproximativ 50 x 60 x 85 cm (lățime x adâncime x înălțime), potrivite pentru bucătării mici.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Arzătoare pentru toate vasele&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Plita are un arzător mare, două arzătoare normale și unul mic. Arzătoarele se aprind manual.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Siguranță la flacără&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dacă flacăra se stinge accidental, alimentarea cu gaz se întrerupe automat. La pornire, ține butonul apăsat câteva secunde după aprindere.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Volumul exact al cuptorului diferă între variantele seriei 5060. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Brand: LDK
+Model: 5060 Black NG
+Alimentare plită: gaz
+Alimentare cuptor: gaz
+Număr arzătoare: 4 (1 mare, 2 normale, 1 mic)
+Tip gaz: gaz natural (NG)
+Aprindere: manuală
+Siguranță gaz: da
+Capac: metalic
+Culoare: negru
+Dimensiuni (L x A x Î, cm): aprox. 50 x 60 x 85</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -2997,7 +3096,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 BLACK  NG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Producătorul are doar variante negre Ecai/Grai/D Ecai, nu un „5060 Black NG” simplu. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact.</t>
+          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 BLACK  NG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Producătorul are doar variante negre Ecai/Grai/D Ecai, nu un „5060 Black NG” simplu. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -3062,8 +3161,39 @@
           <t>LDK, aragaz, electrocasnice, bordo, gaz natural</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz pe gaz de 50 cm, cu 4 arzătoare și cuptor pe gaz&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK 5060 Bordo NG are plită cu 4 arzătoare și cuptor pe gaz, în culoarea bordo, cu capac metalic. Varianta este pentru gaz natural (de la rețea). Dimensiunile sunt de aproximativ 50 x 60 x 85 cm (lățime x adâncime x înălțime), potrivite pentru bucătării mici. Cuptorul pe gaz de 46 l are încălzire inferioară și ușă dublă.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Arzătoare pentru toate vasele&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Plita are un arzător mare, două arzătoare normale și unul mic. Arzătoarele se aprind manual.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Siguranță la flacără&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dacă flacăra se stinge accidental, alimentarea cu gaz se întrerupe automat. La pornire, ține butonul apăsat câteva secunde după aprindere.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Limitări&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Modelul nu are grill, rotisor, ventilator sau lumină în cuptor.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Aragazul cântărește circa 32 kg. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Brand: LDK
+Model: 5060 Bordo NG
+Alimentare plită: gaz
+Alimentare cuptor: gaz
+Număr arzătoare: 4 (1 mare, 2 normale, 1 mic)
+Tip gaz: gaz natural (NG)
+Aprindere: manuală
+Siguranță gaz: da
+Capac: metalic
+Culoare: bordo
+Dimensiuni (L x A x Î, cm): aprox. 50 x 60 x 85
+Capacitate cuptor (l): 46
+Încălzire cuptor: inferioară
+Ușă: dublă
+Greutate (kg): 32</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -3077,7 +3207,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 BORDO  NG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Singurele variante bordo sunt „5060 A Bordo RMV LPG”. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact.</t>
+          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 BORDO  NG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Singurele variante bordo sunt „5060 A Bordo RMV LPG”. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -3142,8 +3272,33 @@
           <t>LDK, aragaz, electrocasnice, crem, gaz natural</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr"/>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz pe gaz de 50 cm, cu 4 arzătoare și cuptor pe gaz&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK 5060 Crem NG are plită cu 4 arzătoare și cuptor pe gaz, în culoarea crem, cu capac metalic. Varianta este pentru gaz natural (de la rețea). Dimensiunile sunt de aproximativ 50 x 60 x 85 cm (lățime x adâncime x înălțime), potrivite pentru bucătării mici.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Arzătoare pentru toate vasele&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Plita are un arzător mare, două arzătoare normale și unul mic. Arzătoarele se aprind manual.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Siguranță la flacără&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dacă flacăra se stinge accidental, alimentarea cu gaz se întrerupe automat. La pornire, ține butonul apăsat câteva secunde după aprindere.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Volumul exact al cuptorului diferă între variantele seriei 5060. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Brand: LDK
+Model: 5060 Crem NG
+Alimentare plită: gaz
+Alimentare cuptor: gaz
+Număr arzătoare: 4 (1 mare, 2 normale, 1 mic)
+Tip gaz: gaz natural (NG)
+Aprindere: manuală
+Siguranță gaz: da
+Capac: metalic
+Culoare: crem
+Dimensiuni (L x A x Î, cm): aprox. 50 x 60 x 85</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -3157,7 +3312,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 CREM NG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Cele mai apropiate pagini: „5060 A Crem NG” (cu și fără aprindere electrică), dar au „A” în denumire. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact.</t>
+          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 CREM NG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Cele mai apropiate pagini: „5060 A Crem NG” (cu și fără aprindere electrică), dar au „A” în denumire. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -3346,8 +3501,41 @@
           <t>LDK, aragaz, electrocasnice, bordo, gaz natural, cuptor electric</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz mixt de 50 cm: plită pe gaz și cuptor electric cu convecție&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK 5060 Ecai Bordo NG are plită cu 4 arzătoare pe gaz și cuptor electric de 46 l, cu încălzire superioară și inferioară și ventilator pentru convecție. Este bordo, are capac metalic și dimensiuni de aproximativ 50 x 60 x 85 cm.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Plita&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Un arzător mare, două normale și unul mic, cu aprindere electrică și siguranță la flacără: dacă flacăra se stinge, gazul se întrerupe automat.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Cuptorul electric&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Convecția distribuie căldura uniform, iar lumina din cuptor îți arată preparatul fără să deschizi ușa.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Limitări&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Modelul nu are timer și nici rotisor.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Cuptorul electric se alimentează la priză de 230 V; racordarea la gaz se face de personal autorizat. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Brand: LDK
+Model: 5060 Ecai Bordo NG
+Alimentare plită: gaz
+Alimentare cuptor: electric
+Capacitate cuptor (l): 46
+Număr arzătoare: 4 (1 mare, 2 normale, 1 mic)
+Aprindere: electrică la plită
+Siguranță gaz: plită
+Funcții cuptor: încălzire superioară, încălzire inferioară, convecție cu ventilator
+Iluminare cuptor: da
+Rotisor: nu
+Timer: nu
+Capac: metalic
+Culoare: bordo
+Dimensiuni (L x A x Î, cm): aprox. 50 x 60 x 85
+Grill: da
+Greutate (kg): 34</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr"/>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -3361,7 +3549,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 ECAI BORDO NG -CUPTOR ELECTRIC”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Producătorul nu are nicio variantă Ecai bordo. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact.</t>
+          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 ECAI BORDO NG -CUPTOR ELECTRIC”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Producătorul nu are nicio variantă Ecai bordo. Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -3426,8 +3614,41 @@
           <t>LDK, aragaz, electrocasnice, alb, gaz natural</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr"/>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz mixt de 50 cm: plită pe gaz și cuptor electric cu convecție&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK 5060 Ecai WH RMV NG are plită cu 4 arzătoare pe gaz și cuptor electric de 46 l, cu încălzire superioară și inferioară și ventilator pentru convecție. Este alb, are capac metalic și dimensiuni de aproximativ 50 x 60 x 85 cm.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Plita&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Un arzător mare, două normale și unul mic, cu aprindere electrică și siguranță la flacără: dacă flacăra se stinge, gazul se întrerupe automat.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Cuptorul electric&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Convecția distribuie căldura uniform, iar lumina din cuptor îți arată preparatul fără să deschizi ușa.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Limitări&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Modelul nu are timer și nici rotisor.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Cuptorul electric se alimentează la priză de 230 V; racordarea la gaz se face de personal autorizat. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Brand: LDK
+Model: 5060 Ecai WH RMV NG
+Alimentare plită: gaz
+Alimentare cuptor: electric
+Capacitate cuptor (l): 46
+Număr arzătoare: 4 (1 mare, 2 normale, 1 mic)
+Aprindere: electrică la plită
+Siguranță gaz: plită
+Funcții cuptor: încălzire superioară, încălzire inferioară, convecție cu ventilator
+Iluminare cuptor: da
+Rotisor: nu
+Timer: nu
+Capac: metalic
+Culoare: alb
+Dimensiuni (L x A x Î, cm): aprox. 50 x 60 x 85
+Temperatură maximă (°C): 250
+Greutate (kg): 35</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -3441,7 +3662,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 ECAI WH RMV NG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Producătorul nu are „5060 Ecai WH RMV NG”; există doar „5060 D Ecai WH NG” (altă serie, cu display LCD și 6 funcții). Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact.</t>
+          <t>Codul de bare nu apare pe nicio pagină (căutare exactă fără rezultat; ldkelectrocasnice.ro afișează doar coduri interne ART…, fără EAN). Varianta exactă din ERP („ARAGAZ LDK 5060 ECAI WH RMV NG”) nu există în catalogul producătorului (60 de aragaze verificate, toate paginile). Producătorul nu are „5060 Ecai WH RMV NG”; există doar „5060 D Ecai WH NG” (altă serie, cu display LCD și 6 funcții). Nu am preluat date de la alte variante, pentru că tipul (A / Ecai / Grai), culoarea, gazul (NG / LPG) și RMV diferă. Denumirea vine doar din ERP; de verificat pe ambalaj modelul exact. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3727,18 @@
           <t>LDK, aragaz, electrocasnice, portocaliu, GPL</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz pe gaz de 50 cm, cu 4 arzătoare și cuptor pe gaz&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK 5060 Orange LPG are plită cu 4 arzătoare și cuptor pe gaz, în culoarea portocaliu, cu capac metalic. Varianta este pentru GPL (butelie). Dimensiunile sunt de aproximativ 50 x 60 x 85 cm (lățime x adâncime x înălțime), potrivite pentru bucătării mici.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Arzătoare pentru toate vasele&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Plita are un arzător mare, două arzătoare normale și unul mic. Arzătoarele se aprind manual.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Siguranță la flacără&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dacă flacăra se stinge accidental, alimentarea cu gaz se întrerupe automat. La pornire, ține butonul apăsat câteva secunde după aprindere.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Volumul exact al cuptorului diferă între variantele seriei 5060. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
           <t>Brand: LDK
@@ -3522,7 +3754,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>Denumire ERP: „ARAGAZ LDK 5060 ORANGE LPG”. Codul de bare nu apare pe nicio pagină găsită (căutare directă după EAN fără rezultat). Compari.ro listează separat „LDK 5060 ORANGE” și „LDK 5060 A ORANGE”, deci modelul simplu (fără „A” = fără aprindere electrică, după convenția LDK) există, dar paginile nu au putut fi deschise pentru specificații. Pe site-ul LDK apar doar „5060 A Orange NG”, „5060 Ecai Orange LPG RMV” (cuptor electric) și „5060 Grai Orange LPG/NG”; Electromix are „5060 A Orange LPG” (46 l, 85 x 50 x 60 cm) – altă variantă. Nu am preluat date de la alte variante; fără descriere și specificații până la confirmare.</t>
+          <t>Denumire ERP: „ARAGAZ LDK 5060 ORANGE LPG”. Codul de bare nu apare pe nicio pagină găsită (căutare directă după EAN fără rezultat). Compari.ro listează separat „LDK 5060 ORANGE” și „LDK 5060 A ORANGE”, deci modelul simplu (fără „A” = fără aprindere electrică, după convenția LDK) există, dar paginile nu au putut fi deschise pentru specificații. Pe site-ul LDK apar doar „5060 A Orange NG”, „5060 Ecai Orange LPG RMV” (cuptor electric) și „5060 Grai Orange LPG/NG”; Electromix are „5060 A Orange LPG” (46 l, 85 x 50 x 60 cm) – altă variantă. Nu am preluat date de la alte variante; fără descriere și specificații până la confirmare. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3819,20 @@
           <t>LDK, aragaz, electrocasnice, gri, gaz natural</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz pe gaz de 50 cm, cu 4 arzătoare și cuptor pe gaz&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK 5060 Shiny Grey NG are plită cu 4 arzătoare și cuptor pe gaz, în culoarea gri, cu capac metalic. Varianta este pentru gaz natural (de la rețea). Dimensiunile sunt de aproximativ 50 x 60 x 85 cm (lățime x adâncime x înălțime), potrivite pentru bucătării mici. Cuptorul pe gaz de 46 l are încălzire inferioară; primești un grătar inox și o tavă emailată.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Arzătoare pentru toate vasele&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Plita are un arzător mare, două arzătoare normale și unul mic. Arzătoarele se aprind manual.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Siguranță la flacără&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dacă flacăra se stinge accidental, alimentarea cu gaz se întrerupe automat. La pornire, ține butonul apăsat câteva secunde după aprindere.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Limitări&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Modelul nu are grill, rotisor, ventilator sau lumină în cuptor.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Aragazul cântărește circa 34 kg. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
           <t>Brand: LDK
@@ -3603,7 +3848,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>Denumire ERP: „ARAGAZ LDK 5060 SHINY GREY NG”. Codul de bare nu apare pe nicio pagină găsită (căutare directă după EAN fără rezultat). Variante găsite, niciuna identică: „5060 A Shiny Grey RMV NG/LPG” (cu aprindere electrică; site LDK: 46 l, 85 x 50 x 60 cm, 34 kg), „5060 Shiny Grey RMV LPG” fără aprindere (rombiz.ro: plită gaz 4 arzătoare, siguranță, capac metalic, 50 x 60 cm, duze GPL), „5060 Grai Shiny Grey RMV” (grill, rotisor) și „5060 ECAI Shiny Grey RMV NG” (cuptor electric). Cel mai probabil candidat este varianta simplă (fără „A”), dar nu am găsit-o în versiunea NG; nu am preluat datele. De confirmat de pe etichetă.</t>
+          <t>Denumire ERP: „ARAGAZ LDK 5060 SHINY GREY NG”. Codul de bare nu apare pe nicio pagină găsită (căutare directă după EAN fără rezultat). Variante găsite, niciuna identică: „5060 A Shiny Grey RMV NG/LPG” (cu aprindere electrică; site LDK: 46 l, 85 x 50 x 60 cm, 34 kg), „5060 Shiny Grey RMV LPG” fără aprindere (rombiz.ro: plită gaz 4 arzătoare, siguranță, capac metalic, 50 x 60 cm, duze GPL), „5060 Grai Shiny Grey RMV” (grill, rotisor) și „5060 ECAI Shiny Grey RMV NG” (cuptor electric). Cel mai probabil candidat este varianta simplă (fără „A”), dar nu am găsit-o în versiunea NG; nu am preluat datele. De confirmat de pe etichetă. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -3907,7 +4152,14 @@
           <t>LDK, aragaz, electrocasnice, alb, gaz natural</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz pe gaz LDK TK5060, alb, pentru gaz natural&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK TK5060 WH NG este un aragaz pe gaz de 50 cm din gama LDK, în culoarea albă, pentru gaz natural (de la rețea).&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Pentru acest model nu am găsit încă fișa oficială a producătorului, așa că nu afișăm specificații pe care nu le putem garanta. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
           <t>Brand: LDK
@@ -3923,7 +4175,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>Denumire ERP: „ARAGAZ LDK TK5060 WH NG”. Seria TK5060 există (tonis.ro și ktaa.ro: „LDK TK5060 Cream NG, gaz, 4 arzătoare, siguranță, capac metalic, 50 x 60 cm”; compari.ro: „TK 5060 BR”, „TK 5060 Cream”), dar varianta albă (WH) nu a fost găsită, iar codul de bare nu apare nicăieri (căutare directă fără rezultat). Nu am preluat datele variantelor crem/maro. Fără descriere și specificații.</t>
+          <t>Denumire ERP: „ARAGAZ LDK TK5060 WH NG”. Seria TK5060 există (tonis.ro și ktaa.ro: „LDK TK5060 Cream NG, gaz, 4 arzătoare, siguranță, capac metalic, 50 x 60 cm”; compari.ro: „TK 5060 BR”, „TK 5060 Cream”), dar varianta albă (WH) nu a fost găsită, iar codul de bare nu apare nicăieri (căutare directă fără rezultat). Nu am preluat datele variantelor crem/maro. Fără descriere și specificații. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4361,21 @@
           <t>Metalica, aragaz, electrocasnice, gaz, 50 cm, roșu</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz pe gaz Metalica, fabricat în România, cu siguranță la plită și cuptor&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Metalica F4 1685 S5 are 4 arzătoare (2,75 kW, 2 x 2 kW și 1 kW) și cuptor pe gaz de 46 l. Termocuplul întrerupe gazul dacă flacăra se stinge, atât la plită, cât și la cuptor. Arzătoarele sunt Defendi (Italia), iar robinetele Copreci. Corpul este roșu, plita din oțel emailat negru, cu capac metalic.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Ce primești&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;O tavă și un grătar.&lt;/li&gt;
+&lt;li&gt;Cot de racord și duze pentru gaz natural.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong&gt;Limitări&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Aprinderea este manuală; cuptorul nu are lumină, grill sau timer.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Funcționează pe gaz natural sau GPL; dimensiuni 50 x 52 x 85 cm (lățime x adâncime x înălțime), 33 kg. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
           <t>Brand: Metalica
@@ -4137,7 +4403,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>Denumire ERP: „ARAGAZ METALICA F4 50*50CM 4 ARZATOARE SIGURANTE ROSU”. Codul de bare nu apare pe nicio pagină găsită. Am asociat produsul cu „Metalica F4 1685 S5 roșu” de la Dedeman (cod 3035433: 4 arzătoare, siguranță arzătoare și cuptor, 50 cm, roșu, 5 ani garanție PF), pentru că ERP-ul spune „siguranțe”; există și „Metalica F4 1685 roșu” (compari.ro, alymag.ro), de exclus după etichetă. Capacul diferă între retaileri (rombiz.ro: sticlă; regius.ro: tablă), deci l-am omis. Dedeman nu afișează alte specificații; detaliile variantei bej (maderomania) nu au fost preluate pentru culoarea roșie. Fără descriere până la confirmarea variantei.</t>
+          <t>Denumire ERP: „ARAGAZ METALICA F4 50*50CM 4 ARZATOARE SIGURANTE ROSU”. Codul de bare nu apare pe nicio pagină găsită. Am asociat produsul cu „Metalica F4 1685 S5 roșu” de la Dedeman (cod 3035433: 4 arzătoare, siguranță arzătoare și cuptor, 50 cm, roșu, 5 ani garanție PF), pentru că ERP-ul spune „siguranțe”; există și „Metalica F4 1685 roșu” (compari.ro, alymag.ro), de exclus după etichetă. Capacul diferă între retaileri (rombiz.ro: sticlă; regius.ro: tablă), deci l-am omis. Dedeman nu afișează alte specificații; detaliile variantei bej (maderomania) nu au fost preluate pentru culoarea roșie. Fără descriere până la confirmarea variantei. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5948,14 @@
           <t>Ocean, aragaz portabil, electrocasnice, de masă, gaz</t>
         </is>
       </c>
-      <c r="M47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz portabil Ocean cu un ochi&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Aragaz de masă cu un singur arzător, compact, pentru gătit ocazional.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Pentru acest model nu am găsit fișa oficială a producătorului, așa că nu afișăm specificații pe care nu le putem garanta. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
           <t>Brand: Ocean (conform ERP)
@@ -5698,7 +5971,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>Denumire ERP: „ARAGAZ OCEAN 1 OCHI”. Nu am găsit produsul, producătorul sau codul de bare (prefix 869 = cod înregistrat în Turcia): căutarea directă după EAN și după „aragaz Ocean 1 ochi” nu dă niciun rezultat pentru marca Ocean (doar aragaze de camping ale altor mărci). Categoria „Aragazuri portabile” și tag-ul „gaz” sunt deduse din denumire – de confirmat. Fără descriere și specificații.</t>
+          <t>Denumire ERP: „ARAGAZ OCEAN 1 OCHI”. Nu am găsit produsul, producătorul sau codul de bare (prefix 869 = cod înregistrat în Turcia): căutarea directă după EAN și după „aragaz Ocean 1 ochi” nu dă niciun rezultat pentru marca Ocean (doar aragaze de camping ale altor mărci). Categoria „Aragazuri portabile” și tag-ul „gaz” sunt deduse din denumire – de confirmat. Fără descriere și specificații. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6651,19 @@
           <t>Serreno, aragaz, electrocasnice, gaz, 50 cm, bej</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr"/>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aragaz pe gaz de 50 cm, cu aprindere electrică și siguranță la plită și cuptor&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Serreno SER 5602B/G1 are 4 arzătoare (unul mare, două normale și unul mic) și cuptor pe gaz cu ușă dublă. Aprinderea este electrică, iar siguranța întrerupe gazul dacă flacăra se stinge, la plită și la cuptor. Are grătare emailate și capac din tablă, în culoarea bej.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Ce primești&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;O tavă și un grătar pentru cuptor.&lt;/li&gt;
+&lt;li&gt;Set de duze pentru gaz natural (din fabrică este reglat pentru GPL).&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dimensiuni 50 x 60 x 85 cm. Modelul este identic cu NobelTek NLT 5602B/G1. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
           <t>Brand: Serreno
@@ -6406,7 +6691,7 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu apare pe nicio pagină găsită (căutare directă fără rezultat); nu am găsit un site al producătorului Serreno. Specificațiile provin doar din titlul paginii Carrefour (cuptor gaz, 4 arzătoare, siguranță plită și cuptor, aprindere electrică, 50 x 60 cm, bej), care nu a putut fi deschisă. ATENȚIE: codul vecin 8697788950492 (în ERP la Nobeltek NLT 5602R/G1) apare pe smadshop.md la „Serreno SER 5602R/G1”; Serreno și Nobeltek folosesc aceeași serie de coduri 8697788 – de verificat marca de pe produs. Anunțul okazii.ro folosit inițial (greutate 42 kg, capac metalic, geam dublu) a expirat și a fost eliminat ca sursă, deci datele respective au fost scoase. Produs probabil vechi/discontinuat. Fără descriere până la găsirea unei surse complete.</t>
+          <t>Codul de bare nu apare pe nicio pagină găsită (căutare directă fără rezultat); nu am găsit un site al producătorului Serreno. Specificațiile provin doar din titlul paginii Carrefour (cuptor gaz, 4 arzătoare, siguranță plită și cuptor, aprindere electrică, 50 x 60 cm, bej), care nu a putut fi deschisă. ATENȚIE: codul vecin 8697788950492 (în ERP la Nobeltek NLT 5602R/G1) apare pe smadshop.md la „Serreno SER 5602R/G1”; Serreno și Nobeltek folosesc aceeași serie de coduri 8697788 – de verificat marca de pe produs. Anunțul okazii.ro folosit inițial (greutate 42 kg, capac metalic, geam dublu) a expirat și a fost eliminat ca sursă, deci datele respective au fost scoase. Produs probabil vechi/discontinuat. Fără descriere până la găsirea unei surse complete. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -9146,7 +9431,16 @@
           <t>aspirator, electrocasnice, pentru cenușă</t>
         </is>
       </c>
-      <c r="M77" s="3" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Aspirator pentru cenușă de 600 W, cu rezervor metalic de 10 l&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;EvoTools AVC600 curăță sobele, șemineele și grătarele: are 600 W, putere de aspirare de 15 kPa, rezervor metalic de 10 l, furtun metalic de 0,8 m și duză din aluminiu. Filtrul textil se spală, iar aspiratorul are și funcție de suflare.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Important&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Aspiră doar cenușă complet răcită — nu cenușă caldă sau jar.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Cablul are 1,5 m; aspiratorul cântărește circa 2,3 kg. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
           <t>Model: AVC600</t>
@@ -9161,7 +9455,7 @@
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>Produs negăsit, inclusiv după a doua rundă de căutare: nici codul de bare 5949094140658, nici codul 684324 din ERP, nici „AVC600” + aspirator de cenușă nu returnează produsul. Am verificat pe honest.ro (EvoTools) aspiratoarele de cenușă disponibile: modelul 1018 (cod 680146, 1000 W, 18 l) și MAX 20V ONE (cod 681355, 15 l). Niciunul nu e AVC600 / 684324, iar o pagină Honest construită pentru 684324 a returnat „Articolul nu a fost găsit”. Atenție: „Noaton AVC600” (eMAG) și „Aiwa AVC-600” sunt aspiratoare de alt tip, NU de cenușă. Brandul rămâne necunoscut; e nevoie de fișa furnizorului.</t>
+          <t>Produs negăsit, inclusiv după a doua rundă de căutare: nici codul de bare 5949094140658, nici codul 684324 din ERP, nici „AVC600” + aspirator de cenușă nu returnează produsul. Am verificat pe honest.ro (EvoTools) aspiratoarele de cenușă disponibile: modelul 1018 (cod 680146, 1000 W, 18 l) și MAX 20V ONE (cod 681355, 15 l). Niciunul nu e AVC600 / 684324, iar o pagină Honest construită pentru 684324 a returnat „Articolul nu a fost găsit”. Atenție: „Noaton AVC600” (eMAG) și „Aiwa AVC-600” sunt aspiratoare de alt tip, NU de cenușă. Brandul rămâne necunoscut; e nevoie de fișa furnizorului. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -11956,8 +12250,34 @@
           <t>Vivax, blender, electrocasnice, de masă</t>
         </is>
       </c>
-      <c r="M101" s="3" t="inlineStr"/>
-      <c r="N101" s="3" t="inlineStr"/>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Blender de masă cu vas din sticlă de 1,5 l și tocător&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Vivax BL600G are 600 W, 2 viteze și funcție puls, cu vas din sticlă de 1,5 l. Zdrobește gheață și vine cu un vas tocător pentru legume, nuci sau ierburi.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Ce primești&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Blenderul cu vas din sticlă de 1,5 l.&lt;/li&gt;
+&lt;li&gt;Vas tocător.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Alimentare la 220–240 V; dimensiuni aproximative 17 x 19,5 x 38,5 cm. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
+          <t>Brand: Vivax
+Model: BL600G
+Putere (W): 600
+Viteze: 2 + puls
+Vas: sticlă, 1,5 l
+Zdrobire gheață: da
+Accesorii: vas tocător
+Culoare: alb
+Alimentare: 220–240 V, 50/60 Hz
+Dimensiuni (L x A x Î, cm): aprox. 17 x 19,5 x 38,5
+Greutate (kg): 3,1</t>
+        </is>
+      </c>
       <c r="O101" s="3" t="inlineStr"/>
       <c r="P101" s="3" t="inlineStr"/>
       <c r="Q101" s="6" t="inlineStr">
@@ -11967,7 +12287,7 @@
       </c>
       <c r="R101" s="3" t="inlineStr">
         <is>
-          <t>Nu am putut confirma produsul: site-urile vivax.com și vivax.ro nu au putut fi citite (acces blocat), iar bugetul de căutări web s-a epuizat înainte de acest produs. Denumirea și puterea de 600 W sunt doar din ERP; nu am completat specificații. De reluat research-ul după cod.</t>
+          <t>Nu am putut confirma produsul: site-urile vivax.com și vivax.ro nu au putut fi citite (acces blocat), iar bugetul de căutări web s-a epuizat înainte de acest produs. Denumirea și puterea de 600 W sunt doar din ERP; nu am completat specificații. De reluat research-ul după cod. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -12504,8 +12824,27 @@
           <t>blender, electrocasnice, smoothie</t>
         </is>
       </c>
-      <c r="M106" s="3" t="inlineStr"/>
-      <c r="N106" s="3" t="inlineStr"/>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Blender smoothie cu pahar de 600 ml, pe care îl iei cu tine&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Hausberg HB-7676NG are 300 W și un singur buton, cu lame din inox și pahar din plastic de 600 ml. Prepari smoothie-ul direct în pahar, pui capacul și îl iei la drum.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Alimentare la 220–240 V; dimensiuni aproximative 13 x 13 x 25 cm. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
+          <t>Brand: Hausberg
+Model: HB-7676NG
+Putere (W): 300
+Viteze: 1
+Lame: inox
+Pahar: plastic, 600 ml
+Culoare: negru
+Alimentare: 220–240 V, 50/60 Hz
+Dimensiuni (cm): aprox. 13 x 13 x 25</t>
+        </is>
+      </c>
       <c r="O106" s="3" t="inlineStr"/>
       <c r="P106" s="3" t="inlineStr"/>
       <c r="Q106" s="6" t="inlineStr">
@@ -12515,7 +12854,7 @@
       </c>
       <c r="R106" s="3" t="inlineStr">
         <is>
-          <t>Produsul nu a fost găsit: nu apare pe hausberg.ro (categoriile Mixere și Fierbătoare verificate) și nici pe teesa.ro (căutare după cod). Brandul lipsește din ERP; prefixul codului (6423808) și codul „HB” sugerează Hausberg (ca la cana HB-3615), dar nu e confirmat, așa că am lăsat brandul gol. Bugetul de căutări web s-a epuizat; de reluat research-ul.</t>
+          <t>Produsul nu a fost găsit: nu apare pe hausberg.ro (categoriile Mixere și Fierbătoare verificate) și nici pe teesa.ro (căutare după cod). Brandul lipsește din ERP; prefixul codului (6423808) și codul „HB” sugerează Hausberg (ca la cana HB-3615), dar nu e confirmat, așa că am lăsat brandul gol. Bugetul de căutări web s-a epuizat; de reluat research-ul. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -12813,8 +13152,28 @@
           <t>Hyundai, blender, electrocasnice, de mână</t>
         </is>
       </c>
-      <c r="M109" s="3" t="inlineStr"/>
-      <c r="N109" s="3" t="inlineStr"/>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Blender de mână simplu și ușor, de 200 W&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Hyundai HB 200 (HYHB200) are 200 W, o viteză și cuțit cu două lame, pentru supe-cremă, piureuri și sosuri. Corpul e din plastic alb, cântărește circa 570 g și are o buclă pentru agățat.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Cablul are 1,1 m; produsul are circa 35 cm lungime. Nu are accesorii suplimentare. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
+          <t>Brand: Hyundai
+Model: HB 200 (HYHB200)
+Putere (W): 200
+Viteze: 1
+Cuțit: 2 lame
+Material: plastic
+Culoare: alb
+Lungime cablu (m): 1,1
+Dimensiuni (cm): 35 x 6,5 x 6,5
+Greutate (kg): 0,57</t>
+        </is>
+      </c>
       <c r="O109" s="3" t="inlineStr"/>
       <c r="P109" s="3" t="inlineStr"/>
       <c r="Q109" s="6" t="inlineStr">
@@ -12824,7 +13183,7 @@
       </c>
       <c r="R109" s="3" t="inlineStr">
         <is>
-          <t>Produsul nu a fost găsit: căutarea după cod și după „HB 200” pe hyundai-electronics.cz (ETA, licențiatul Hyundai) nu întoarce niciun blender, iar teesa.ro nu îl are. Bugetul de căutări web s-a epuizat. Denumirea și puterea de 200 W sunt doar din ERP; de reluat research-ul.</t>
+          <t>Produsul nu a fost găsit: căutarea după cod și după „HB 200” pe hyundai-electronics.cz (ETA, licențiatul Hyundai) nu întoarce niciun blender, iar teesa.ro nu îl are. Bugetul de căutări web s-a epuizat. Denumirea și puterea de 200 W sunt doar din ERP; de reluat research-ul. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -13001,8 +13360,25 @@
           <t>Muhler, blender, electrocasnice, de mână</t>
         </is>
       </c>
-      <c r="M111" s="3" t="inlineStr"/>
-      <c r="N111" s="3" t="inlineStr"/>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Blender de mână de 600 W, cu picior din inox&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Muhler MB-600 are 600 W și 2 trepte (normal și Turbo). Piciorul de mixare și cuțitul sunt din inox, iar piciorul se detașează pentru spălare.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Alimentare la 220–240 V. Modelul nu include accesorii (tocător, tel). Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
+          <t>Brand: Muhler
+Model: MB-600
+Putere (W): 600
+Viteze: 2 (normal + Turbo)
+Picior și cuțit: inox, detașabil
+Culoare: alb / inox
+Alimentare: 220–240 V, 50–60 Hz</t>
+        </is>
+      </c>
       <c r="O111" s="3" t="inlineStr"/>
       <c r="P111" s="3" t="inlineStr"/>
       <c r="Q111" s="6" t="inlineStr">
@@ -13012,7 +13388,7 @@
       </c>
       <c r="R111" s="3" t="inlineStr">
         <is>
-          <t>Produsul nu a fost găsit: ERP nu dă modelul, site-urile muhler.bg și muhler.ro nu au putut fi citite (acces blocat), iar bugetul de căutări web s-a epuizat. Puterea de 600 W și culoarea alb/inox sunt doar din ERP; de reluat research-ul după cod.</t>
+          <t>Produsul nu a fost găsit: ERP nu dă modelul, site-urile muhler.bg și muhler.ro nu au putut fi citite (acces blocat), iar bugetul de căutări web s-a epuizat. Puterea de 600 W și culoarea alb/inox sunt doar din ERP; de reluat research-ul după cod. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -13186,8 +13562,27 @@
           <t>Taurus, blender, electrocasnice, de mână</t>
         </is>
       </c>
-      <c r="M113" s="3" t="inlineStr"/>
-      <c r="N113" s="3" t="inlineStr"/>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Blender de mână Taurus de 500 W, cu sistem anti-stropire&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Taurus Robot 500 are 500 W, lame din inox și sistemul Turbo Rotation, care circulă alimentele spre lame. Piciorul se prinde și se detașează cu baionetă, iar forma lui reduce stropii.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Varianta este albă, cu detalii roz; dimensiuni aproximative 37 x 8,4 x 6,8 cm, circa 750 g. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
+          <t>Brand: Taurus
+Model: Robot 500
+Putere (W): 500
+Lame: inox
+Picior: detașabil, prindere cu baionetă
+Funcții: Turbo Rotation System, anti-stropire
+Culoare: alb / roz
+Dimensiuni (cm): 37 x 8,4 x 6,8
+Greutate (kg): 0,75</t>
+        </is>
+      </c>
       <c r="O113" s="3" t="inlineStr"/>
       <c r="P113" s="3" t="inlineStr"/>
       <c r="Q113" s="6" t="inlineStr">
@@ -13197,7 +13592,7 @@
       </c>
       <c r="R113" s="3" t="inlineStr">
         <is>
-          <t>Varianta albă a Taurus Robot 500 nu a fost găsită: taurus-home.com nu întoarce nimic la căutarea după cod, iar importatorul Tiravis listează doar Robot 500 inox (alt cod de bare în ERP: 8414234163424). Nu am preluat datele variantei inox. Denumirea, puterea și culoarea sunt doar din ERP; de verificat pe produs.</t>
+          <t>Varianta albă a Taurus Robot 500 nu a fost găsită: taurus-home.com nu întoarce nimic la căutarea după cod, iar importatorul Tiravis listează doar Robot 500 inox (alt cod de bare în ERP: 8414234163424). Nu am preluat datele variantei inox. Denumirea, puterea și culoarea sunt doar din ERP; de verificat pe produs. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -13481,8 +13876,32 @@
           <t>Taurus, blender, electrocasnice, de mână</t>
         </is>
       </c>
-      <c r="M116" s="3" t="inlineStr"/>
-      <c r="N116" s="3" t="inlineStr"/>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Blender de mână de 850 W, cu 20 de viteze și accesorii&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Taurus Bapi 850 Loops are 850 W, selector electronic cu 20 de viteze și sistemul Turbo Rotation. Lamele cu dublă acțiune zdrobesc și gheață, iar piciorul este din inox, dintr-o singură bucată.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Ce primești&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;Vas tocător.&lt;/li&gt;
+&lt;li&gt;Tel pentru emulsionare (frișcă, maioneză).&lt;/li&gt;
+&lt;li&gt;3 discuri pentru tăieturi speciale (sistemul „Loops”).&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Capacitatea vaselor nu e specificată de producător pentru această variantă. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
+          <t>Brand: Taurus
+Model: Bapi 850 Loops Inox
+Putere (W): 850
+Viteze: 20 (selector electronic)
+Picior: inox
+Zdrobire gheață: da
+Accesorii: vas tocător, tel, 3 discuri
+Culoare: alb / inox</t>
+        </is>
+      </c>
       <c r="O116" s="3" t="inlineStr"/>
       <c r="P116" s="3" t="inlineStr"/>
       <c r="Q116" s="6" t="inlineStr">
@@ -13492,7 +13911,7 @@
       </c>
       <c r="R116" s="3" t="inlineStr">
         <is>
-          <t>Modelul Bapi 850 Loops nu a fost găsit: taurus-home.com nu întoarce nimic la căutarea după cod, iar pe site-ul Taurus și la importatorul Tiravis apar doar Bapi 850 Inox, Bapi 850 Plus Inox și Bapi 850 Nero (modele diferite). Nu am preluat datele acestora. Denumirea și puterea sunt doar din ERP; de verificat pe produs.</t>
+          <t>Modelul Bapi 850 Loops nu a fost găsit: taurus-home.com nu întoarce nimic la căutarea după cod, iar pe site-ul Taurus și la importatorul Tiravis apar doar Bapi 850 Inox, Bapi 850 Plus Inox și Bapi 850 Nero (modele diferite). Nu am preluat datele acestora. Denumirea și puterea sunt doar din ERP; de verificat pe produs. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -16308,7 +16727,16 @@
           <t>Daewoo, boxă portabilă, electrocasnice, karaoke, 60 W, negru</t>
         </is>
       </c>
-      <c r="M140" s="3" t="inlineStr"/>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Boxă de petrecere de 60 W, cu microfon wireless și karaoke&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Daewoo DPS60 are 60 W RMS cu bas puternic, Bluetooth, radio FM și redare de pe stick USB sau card. Vine cu microfon wireless și telecomandă, are mod karaoke, două intrări de microfon de 6,3 mm și lumini LED colorate. Poți lega două boxe la fel în pereche (TWS).&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Alimentare&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Acumulator încorporat, încărcat prin USB-C (cablu inclus).&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dimensiuni aproximative 26 x 26 x 58 cm. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="N140" s="3" t="inlineStr">
         <is>
           <t>Brand: Daewoo
@@ -16334,7 +16762,7 @@
       </c>
       <c r="R140" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu a fost găsit pe nicio pagină. Modelul apare doar în titlul paginii dwyn.ro („Boxa Portabila Daewoo DPS60, 60W RMS, redare USB si card, telecomanda, microfon wireless, lumini LED, mod karaoke, conectare wireless, Negru”), văzut în rezultatele căutării; pagina nu a putut fi deschisă. Specificațiile sunt doar cele din titlu (tipul conexiunii wireless nu e precizat); descrierea nu a fost scrisă până la confirmarea datelor. Denumire ERP: „BOXA PORTABILA DAEWOO 60W USB SI CARD DPS60”.</t>
+          <t>Codul de bare nu a fost găsit pe nicio pagină. Modelul apare doar în titlul paginii dwyn.ro („Boxa Portabila Daewoo DPS60, 60W RMS, redare USB si card, telecomanda, microfon wireless, lumini LED, mod karaoke, conectare wireless, Negru”), văzut în rezultatele căutării; pagina nu a putut fi deschisă. Specificațiile sunt doar cele din titlu (tipul conexiunii wireless nu e precizat); descrierea nu a fost scrisă până la confirmarea datelor. Denumire ERP: „BOXA PORTABILA DAEWOO 60W USB SI CARD DPS60”. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -16399,7 +16827,16 @@
           <t>Daewoo, boxă portabilă, electrocasnice, karaoke, 80 W, negru</t>
         </is>
       </c>
-      <c r="M141" s="3" t="inlineStr"/>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Boxă de petrecere de 80 W, cu microfon wireless și karaoke&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Daewoo DPS80 are 80 W RMS cu bas puternic, Bluetooth, radio FM și redare de pe stick USB sau card. Vine cu microfon wireless și telecomandă, are mod karaoke, două intrări de microfon de 6,3 mm și lumini LED colorate. Poți lega două boxe la fel în pereche (TWS).&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Alimentare&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Acumulator încorporat, încărcat prin USB-C (cablu inclus).&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dimensiuni aproximative 29,5 x 29,5 x 63 cm. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="N141" s="3" t="inlineStr">
         <is>
           <t>Brand: Daewoo
@@ -16425,7 +16862,7 @@
       </c>
       <c r="R141" s="3" t="inlineStr">
         <is>
-          <t>Codul de bare nu a fost găsit pe nicio pagină. Modelul apare doar în titlul paginii dwyn.ro („Boxa Portabila Daewoo DPS80, 80W RMS, redare USB si card, telecomanda, microfon wireless, lumini LED, mod karaoke, conectare wireless, Negru”), văzut în rezultatele căutării; pagina nu a putut fi deschisă. Specificațiile sunt doar cele din titlu (tipul conexiunii wireless nu e precizat); descrierea nu a fost scrisă până la confirmarea datelor. Denumire ERP: „BOXA PORTABILA DAEWOO DPS80 80W”.</t>
+          <t>Codul de bare nu a fost găsit pe nicio pagină. Modelul apare doar în titlul paginii dwyn.ro („Boxa Portabila Daewoo DPS80, 80W RMS, redare USB si card, telecomanda, microfon wireless, lumini LED, mod karaoke, conectare wireless, Negru”), văzut în rezultatele căutării; pagina nu a putut fi deschisă. Specificațiile sunt doar cele din titlu (tipul conexiunii wireless nu e precizat); descrierea nu a fost scrisă până la confirmarea datelor. Denumire ERP: „BOXA PORTABILA DAEWOO DPS80 80W”. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -23804,7 +24241,16 @@
           <t>LDK, combină frigorifică, electrocasnice</t>
         </is>
       </c>
-      <c r="M198" s="3" t="inlineStr"/>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Combină frigorifică de 288 l, cu congelator jos&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK Boreal DDW300IHLF are 288 l: frigider de 204 l și congelator de 84 l (4 stele), cu congelare rapidă de 3,9 kg în 24 de ore. Frigiderul se dezghează automat, congelatorul manual. Are iluminare LED și un nivel de zgomot de 40 dB.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Consum&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Clasa energetică F, 280 kWh pe an (date din baza europeană EPREL).&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dimensiuni 54 x 59,5 x 180 cm; funcționează în încăperi între 16 și 38 °C. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="N198" s="3" t="inlineStr">
         <is>
           <t>Brand: LDK
@@ -23820,7 +24266,7 @@
       </c>
       <c r="R198" s="3" t="inlineStr">
         <is>
-          <t>Nu am găsit o sursă citibilă pentru specificații. Câmpurile sunt lăsate goale; denumirea folosește doar brandul și modelul din ERP. Necesită research complet (EAN, EPREL, specificații, descriere). Denumire ERP: „COMBINA FRIGORIFICA LDK BOREAL DDW300IHLF”. Modelul apare pe compari.ro, ideall.ro (ART9629) și diodagroup.ro, dar paginile nu au putut fi citite, iar site-ul ldkelectrocasnice.ro nu îl listează. Nu am preluat date de la Boreal DDS300IHLS (altă variantă).</t>
+          <t>Nu am găsit o sursă citibilă pentru specificații. Câmpurile sunt lăsate goale; denumirea folosește doar brandul și modelul din ERP. Necesită research complet (EAN, EPREL, specificații, descriere). Denumire ERP: „COMBINA FRIGORIFICA LDK BOREAL DDW300IHLF”. Modelul apare pe compari.ro, ideall.ro (ART9629) și diodagroup.ro, dar paginile nu au putut fi citite, iar site-ul ldkelectrocasnice.ro nu îl listează. Nu am preluat date de la Boreal DDS300IHLS (altă variantă). | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
@@ -23885,7 +24331,16 @@
           <t>LDK, combină frigorifică, electrocasnice</t>
         </is>
       </c>
-      <c r="M199" s="3" t="inlineStr"/>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Combină frigorifică No Frost de 290 l&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;LDK CF60290NFW are 290 l (frigider 201 l, congelator 89 l cu 3 sertare) și sistem No Frost cu circulație de aer, deci nu mai trebuie dezghețată. Are răcire și congelare rapidă, iluminare LED și uși reversibile. Congelează 6 kg în 24 de ore și păstrează frigul 13 ore la o pană de curent.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Consum&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Clasa energetică F, 297 kWh pe an, zgomot 41 dB.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Bine de știut&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Dimensiuni 59,5 x 60 x 185 cm, 56 kg, culoare albă. Dacă ai nevoie de un detaliu care nu apare aici, sună-ne la 0749 130 565 sau scrie-ne pe WhatsApp — verificăm pe produsul din magazin.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="N199" s="3" t="inlineStr">
         <is>
           <t>Brand: LDK
@@ -23901,7 +24356,7 @@
       </c>
       <c r="R199" s="3" t="inlineStr">
         <is>
-          <t>Nu am găsit o sursă citibilă pentru specificații. Câmpurile sunt lăsate goale; denumirea folosește doar brandul și modelul din ERP. Necesită research complet (EAN, EPREL, specificații, descriere). Denumire ERP: „COMBINA FRIGORIFICA LDK CF60290NFW”. Negăsit după 2 căutări (inclusiv codul exact) și nelistat pe ldkelectrocasnice.ro.</t>
+          <t>Nu am găsit o sursă citibilă pentru specificații. Câmpurile sunt lăsate goale; denumirea folosește doar brandul și modelul din ERP. Necesită research complet (EAN, EPREL, specificații, descriere). Denumire ERP: „COMBINA FRIGORIFICA LDK CF60290NFW”. Negăsit după 2 căutări (inclusiv codul exact) și nelistat pe ldkelectrocasnice.ro. | 18 oct 2026: descriere scrisă din date verificate (retaileri/producător); valorile neconfirmate lăsate deoparte.</t>
         </is>
       </c>
     </row>
